--- a/план.xlsx
+++ b/план.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d.sokolov\Desktop\study-summer-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD02B5F7-B731-4810-988A-1ACFA6A2DD3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA04C1CE-599A-46D6-AF70-18799459463B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/план.xlsx
+++ b/план.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d.sokolov\Desktop\study-summer-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA04C1CE-599A-46D6-AF70-18799459463B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F5F06D1-16DC-4738-9FB3-D072EAB06328}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/план.xlsx
+++ b/план.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d.sokolov\Desktop\study-summer-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F5F06D1-16DC-4738-9FB3-D072EAB06328}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6168F618-D486-4339-AF0C-BE081A90773B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Дата сдачи</t>
   </si>
@@ -39,9 +39,6 @@
     <t>Комментарий</t>
   </si>
   <si>
-    <t>Математические методы и модели в экономике</t>
-  </si>
-  <si>
     <t xml:space="preserve">Электронный бизнес </t>
   </si>
   <si>
@@ -57,9 +54,6 @@
     <t xml:space="preserve">Сделать первые 3 лабы в СДО Прометей, отчеты прислать Вике, она архивом отправляет преподу. Решить тест. </t>
   </si>
   <si>
-    <t>Решить задачи к экзамену. Наличие их - оценка 3, обсуждение по задачам - на 4 или 5. При плохом ответе на обсуждении может быть оценка 2.</t>
-  </si>
-  <si>
     <t>Сделать отчеты по практикам, к зачету готовить вопросы.</t>
   </si>
   <si>
@@ -72,9 +66,6 @@
     <t>Статус</t>
   </si>
   <si>
-    <t>Разработка Web-приложений</t>
-  </si>
-  <si>
     <t>курсач со всеми доками должен быть уже у миронова</t>
   </si>
   <si>
@@ -84,16 +75,10 @@
     <t>нет данных, сделал 5 лаб, доделать</t>
   </si>
   <si>
-    <t>пройтись по файлам, все проверить. Выбрать какую 6 лабу сдавать</t>
-  </si>
-  <si>
     <t>Отчеты готовы (проверить) + тест 11.06</t>
   </si>
   <si>
     <t>Курсач готов, проверить. Печать: титульник, курсач, антиплагиат, флешка</t>
-  </si>
-  <si>
-    <t>Переписать + разобрать</t>
   </si>
   <si>
     <t>Преза готова, подготовиться перед экзом</t>
@@ -451,7 +436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.5703125" customWidth="1"/>
@@ -468,7 +453,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -479,99 +464,74 @@
         <v>46177</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="6">
+        <v>46184</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>46184</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
+        <v>46192</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
+        <v>46195</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>6</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
-        <v>46178</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
-        <v>46184</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
-        <v>46184</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>46192</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
-        <v>46192</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
-        <v>46195</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D8">
-    <sortCondition ref="A2:A8"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D6">
+    <sortCondition ref="A2:A6"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
